--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>117955340</v>
       </c>
       <c r="B12" t="n">
-        <v>102146</v>
+        <v>102148</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2060,7 +2060,7 @@
         <v>120862105</v>
       </c>
       <c r="B13" t="n">
-        <v>90120</v>
+        <v>90130</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2297,6 +2297,283 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121421947</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13529</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>250187</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Achalcus bimaculatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pollet, 1996</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>592520</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6275737</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2006-07-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2006-07-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>meadow with shrub vegetation</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121422006</v>
+      </c>
+      <c r="B16" t="n">
+        <v>13866</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101389</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neurigona abdominalis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fallén, 1823)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592520</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6275737</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2005-06-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2005-06-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>meadow with shrub vegetation</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2299,7 +2299,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121421947</v>
+        <v>121421945</v>
       </c>
       <c r="B15" t="n">
         <v>13529</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2299,7 +2299,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121421945</v>
+        <v>121421947</v>
       </c>
       <c r="B15" t="n">
         <v>13529</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2166,7 +2166,7 @@
         <v>121374571</v>
       </c>
       <c r="B14" t="n">
-        <v>18262</v>
+        <v>18265</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121421947</v>
+        <v>121422006</v>
       </c>
       <c r="B15" t="n">
-        <v>13529</v>
+        <v>13869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,16 +2315,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>250187</v>
+        <v>101389</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Achalcus bimaculatus</t>
+          <t>Neurigona abdominalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pollet, 1996</t>
+          <t>(Fallén, 1823)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2388,12 +2393,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2006-07-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2006-07-20</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121422006</v>
+        <v>121421947</v>
       </c>
       <c r="B16" t="n">
-        <v>13866</v>
+        <v>13532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2451,21 +2456,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101389</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Gulbakig trädstyltfluga</t>
-        </is>
+        <v>250187</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neurigona abdominalis</t>
+          <t>Achalcus bimaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fallén, 1823)</t>
+          <t>Pollet, 1996</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-07-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2299,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121422006</v>
+        <v>121421947</v>
       </c>
       <c r="B15" t="n">
-        <v>13869</v>
+        <v>13532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,21 +2315,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101389</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Gulbakig trädstyltfluga</t>
-        </is>
+        <v>250187</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neurigona abdominalis</t>
+          <t>Achalcus bimaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fallén, 1823)</t>
+          <t>Pollet, 1996</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2393,12 +2388,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121421947</v>
+        <v>121422006</v>
       </c>
       <c r="B16" t="n">
-        <v>13532</v>
+        <v>13869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2456,16 +2451,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>250187</v>
+        <v>101389</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Achalcus bimaculatus</t>
+          <t>Neurigona abdominalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pollet, 1996</t>
+          <t>(Fallén, 1823)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2006-07-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2006-07-20</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121421947</v>
+        <v>121422006</v>
       </c>
       <c r="B15" t="n">
-        <v>13532</v>
+        <v>13869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,16 +2315,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>250187</v>
+        <v>101389</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Achalcus bimaculatus</t>
+          <t>Neurigona abdominalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pollet, 1996</t>
+          <t>(Fallén, 1823)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2388,12 +2393,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2006-07-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2006-07-20</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121422006</v>
+        <v>121421947</v>
       </c>
       <c r="B16" t="n">
-        <v>13869</v>
+        <v>13532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2451,21 +2456,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101389</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Gulbakig trädstyltfluga</t>
-        </is>
+        <v>250187</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neurigona abdominalis</t>
+          <t>Achalcus bimaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fallén, 1823)</t>
+          <t>Pollet, 1996</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-07-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2569,6 +2569,156 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121580129</v>
+      </c>
+      <c r="B17" t="n">
+        <v>30220</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102645</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ängsvägstekel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Priocnemis agilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Shuckard, 1837)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592520</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6275737</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2003-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2003-08-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>meadow with shrub vegetation</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Johan Abenius</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Svenska Malaisefälleprojektet</t>
         </is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2576,7 +2576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121580129</v>
+        <v>121580128</v>
       </c>
       <c r="B17" t="n">
         <v>30220</v>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2003-08-07</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2003-08-18</t>
+          <t>2004-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121422006</v>
+        <v>121421945</v>
       </c>
       <c r="B15" t="n">
-        <v>13869</v>
+        <v>13532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,21 +2315,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101389</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Gulbakig trädstyltfluga</t>
-        </is>
+        <v>250187</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neurigona abdominalis</t>
+          <t>Achalcus bimaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fallén, 1823)</t>
+          <t>Pollet, 1996</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2349,7 +2344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2393,12 +2388,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121421947</v>
+        <v>121422006</v>
       </c>
       <c r="B16" t="n">
-        <v>13532</v>
+        <v>13869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2456,16 +2451,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>250187</v>
+        <v>101389</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Achalcus bimaculatus</t>
+          <t>Neurigona abdominalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pollet, 1996</t>
+          <t>(Fallén, 1823)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2006-07-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2006-07-20</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2719,6 +2719,151 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121603374</v>
+      </c>
+      <c r="B18" t="n">
+        <v>13427</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>236243</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Myopa hirsuta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Stuke &amp; Clements, 2008</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592520</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6275737</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2005-04-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2005-05-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>meadow with shrub vegetation</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Fredrik Östrand</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Svenska Malaisefälleprojektet</t>
         </is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2299,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121421945</v>
+        <v>121422006</v>
       </c>
       <c r="B15" t="n">
-        <v>13532</v>
+        <v>13869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,16 +2315,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>250187</v>
+        <v>101389</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Achalcus bimaculatus</t>
+          <t>Neurigona abdominalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pollet, 1996</t>
+          <t>(Fallén, 1823)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2344,7 +2349,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2388,12 +2393,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2006-07-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2006-07-20</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121422006</v>
+        <v>121421945</v>
       </c>
       <c r="B16" t="n">
-        <v>13869</v>
+        <v>13532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2451,21 +2456,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101389</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Gulbakig trädstyltfluga</t>
-        </is>
+        <v>250187</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neurigona abdominalis</t>
+          <t>Achalcus bimaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fallén, 1823)</t>
+          <t>Pollet, 1996</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-07-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2299,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121422006</v>
+        <v>121421945</v>
       </c>
       <c r="B15" t="n">
-        <v>13869</v>
+        <v>13532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,21 +2315,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101389</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Gulbakig trädstyltfluga</t>
-        </is>
+        <v>250187</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neurigona abdominalis</t>
+          <t>Achalcus bimaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fallén, 1823)</t>
+          <t>Pollet, 1996</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2349,7 +2344,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2393,12 +2388,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121421945</v>
+        <v>121422006</v>
       </c>
       <c r="B16" t="n">
-        <v>13532</v>
+        <v>13869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2456,16 +2451,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>250187</v>
+        <v>101389</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Achalcus bimaculatus</t>
+          <t>Neurigona abdominalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pollet, 1996</t>
+          <t>(Fallén, 1823)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2006-07-03</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2006-07-20</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2576,7 +2576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121580128</v>
+        <v>121580129</v>
       </c>
       <c r="B17" t="n">
         <v>30220</v>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2003-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2004-08-23</t>
+          <t>2003-08-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2166,7 +2166,7 @@
         <v>121374571</v>
       </c>
       <c r="B14" t="n">
-        <v>18265</v>
+        <v>18266</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>121421945</v>
       </c>
       <c r="B15" t="n">
-        <v>13532</v>
+        <v>13533</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>121422006</v>
       </c>
       <c r="B16" t="n">
-        <v>13869</v>
+        <v>13870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121580128</v>
+        <v>121580129</v>
       </c>
       <c r="B17" t="n">
-        <v>30220</v>
+        <v>30221</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2003-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2004-08-23</t>
+          <t>2003-08-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -2729,7 +2729,7 @@
         <v>121603374</v>
       </c>
       <c r="B18" t="n">
-        <v>13427</v>
+        <v>13428</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2869,6 +2869,156 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121861066</v>
+      </c>
+      <c r="B19" t="n">
+        <v>24791</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102058</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stumpvingeharkrank</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tipula autumnalis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Loew, 1864</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592520</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6275737</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2006-08-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2006-09-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>meadow with shrub vegetation</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2576,7 +2576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121580129</v>
+        <v>121580128</v>
       </c>
       <c r="B17" t="n">
         <v>30221</v>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2003-08-07</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2003-08-18</t>
+          <t>2004-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2576,7 +2576,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121580128</v>
+        <v>121580129</v>
       </c>
       <c r="B17" t="n">
         <v>30221</v>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2003-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2004-08-23</t>
+          <t>2003-08-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2579,7 +2579,7 @@
         <v>121580128</v>
       </c>
       <c r="B17" t="n">
-        <v>30221</v>
+        <v>30226</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>121861066</v>
       </c>
       <c r="B19" t="n">
-        <v>24791</v>
+        <v>24794</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -2874,7 +2874,7 @@
         <v>121861066</v>
       </c>
       <c r="B19" t="n">
-        <v>24794</v>
+        <v>24795</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3019,6 +3019,459 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122845685</v>
+      </c>
+      <c r="B20" t="n">
+        <v>110272</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gamla skogsby, Station Linné, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592472</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6275775</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122845675</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8355</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gamla skogsby, Station Linné, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>592472</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6275775</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122845682</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106009</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gamla skogsby, Station Linné, Öl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>592472</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6275775</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122845740</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100613</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gamla skogsby, Station Linné, Öl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>592472</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6275775</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845685</v>
+        <v>122845740</v>
       </c>
       <c r="B20" t="n">
-        <v>110272</v>
+        <v>100621</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3037,26 +3037,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -3132,10 +3140,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845675</v>
+        <v>122845685</v>
       </c>
       <c r="B21" t="n">
-        <v>8355</v>
+        <v>110280</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3144,32 +3152,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106540</v>
+        <v>219677</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3247,7 +3254,7 @@
         <v>122845682</v>
       </c>
       <c r="B22" t="n">
-        <v>106009</v>
+        <v>106017</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3355,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845740</v>
+        <v>122845675</v>
       </c>
       <c r="B23" t="n">
-        <v>100613</v>
+        <v>8355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3367,39 +3374,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845740</v>
+        <v>122845675</v>
       </c>
       <c r="B20" t="n">
-        <v>100621</v>
+        <v>8355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,39 +3033,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3362,10 +3355,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845675</v>
+        <v>122845740</v>
       </c>
       <c r="B23" t="n">
-        <v>8355</v>
+        <v>100621</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3374,32 +3367,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3133,10 +3133,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845685</v>
+        <v>122845682</v>
       </c>
       <c r="B21" t="n">
-        <v>110280</v>
+        <v>106019</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3145,20 +3145,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219677</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3244,10 +3244,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845682</v>
+        <v>122845740</v>
       </c>
       <c r="B22" t="n">
-        <v>106017</v>
+        <v>100623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3256,30 +3256,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
@@ -3355,10 +3363,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845740</v>
+        <v>122845685</v>
       </c>
       <c r="B23" t="n">
-        <v>100621</v>
+        <v>110282</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3371,34 +3379,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845675</v>
+        <v>122845685</v>
       </c>
       <c r="B20" t="n">
-        <v>8355</v>
+        <v>110282</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,32 +3033,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106540</v>
+        <v>219677</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3133,10 +3132,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845682</v>
+        <v>122845675</v>
       </c>
       <c r="B21" t="n">
-        <v>106019</v>
+        <v>8355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3145,31 +3144,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845740</v>
+        <v>122845682</v>
       </c>
       <c r="B22" t="n">
-        <v>100623</v>
+        <v>106019</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3256,38 +3256,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
@@ -3363,10 +3355,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845685</v>
+        <v>122845740</v>
       </c>
       <c r="B23" t="n">
-        <v>110282</v>
+        <v>100623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3379,26 +3371,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845685</v>
+        <v>122845682</v>
       </c>
       <c r="B20" t="n">
-        <v>110282</v>
+        <v>106027</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,20 +3033,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219677</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3132,10 +3132,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845675</v>
+        <v>122845740</v>
       </c>
       <c r="B21" t="n">
-        <v>8355</v>
+        <v>100631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3144,32 +3144,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3244,10 +3251,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845682</v>
+        <v>122845685</v>
       </c>
       <c r="B22" t="n">
-        <v>106019</v>
+        <v>110290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3256,20 +3263,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>219677</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3355,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845740</v>
+        <v>122845675</v>
       </c>
       <c r="B23" t="n">
-        <v>100623</v>
+        <v>8355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3367,39 +3374,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845682</v>
+        <v>122845740</v>
       </c>
       <c r="B20" t="n">
-        <v>106027</v>
+        <v>100631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,30 +3033,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -3132,10 +3140,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845740</v>
+        <v>122845682</v>
       </c>
       <c r="B21" t="n">
-        <v>100631</v>
+        <v>106027</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3144,38 +3152,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845740</v>
+        <v>122845675</v>
       </c>
       <c r="B20" t="n">
-        <v>100631</v>
+        <v>8355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,39 +3033,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3140,10 +3133,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845682</v>
+        <v>122845740</v>
       </c>
       <c r="B21" t="n">
-        <v>106027</v>
+        <v>100631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3152,30 +3145,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -3251,10 +3252,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845685</v>
+        <v>122845682</v>
       </c>
       <c r="B22" t="n">
-        <v>110290</v>
+        <v>106027</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3263,20 +3264,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219677</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3362,10 +3363,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845675</v>
+        <v>122845685</v>
       </c>
       <c r="B23" t="n">
-        <v>8355</v>
+        <v>110290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3374,32 +3375,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106540</v>
+        <v>219677</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3133,10 +3133,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845740</v>
+        <v>122845685</v>
       </c>
       <c r="B21" t="n">
-        <v>100631</v>
+        <v>110290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3149,34 +3149,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -3363,10 +3355,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845685</v>
+        <v>122845740</v>
       </c>
       <c r="B23" t="n">
-        <v>110290</v>
+        <v>100631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3379,26 +3371,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3133,10 +3133,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845685</v>
+        <v>122845740</v>
       </c>
       <c r="B21" t="n">
-        <v>110290</v>
+        <v>100634</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3149,26 +3149,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -3244,10 +3252,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845682</v>
+        <v>122845685</v>
       </c>
       <c r="B22" t="n">
-        <v>106027</v>
+        <v>110296</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3256,20 +3264,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>219677</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3355,10 +3363,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845740</v>
+        <v>122845682</v>
       </c>
       <c r="B23" t="n">
-        <v>100631</v>
+        <v>106030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3367,38 +3375,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845675</v>
+        <v>122845740</v>
       </c>
       <c r="B20" t="n">
-        <v>8355</v>
+        <v>100636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,32 +3033,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3133,10 +3140,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845740</v>
+        <v>122845685</v>
       </c>
       <c r="B21" t="n">
-        <v>100634</v>
+        <v>110298</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3149,34 +3156,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -3252,10 +3251,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845685</v>
+        <v>122845682</v>
       </c>
       <c r="B22" t="n">
-        <v>110296</v>
+        <v>106032</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3264,20 +3263,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219677</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3363,10 +3362,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845682</v>
+        <v>122845675</v>
       </c>
       <c r="B23" t="n">
-        <v>106030</v>
+        <v>8355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3375,31 +3374,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -3021,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845740</v>
+        <v>122845682</v>
       </c>
       <c r="B20" t="n">
-        <v>100636</v>
+        <v>106038</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,38 +3033,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -3140,10 +3132,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845685</v>
+        <v>122845675</v>
       </c>
       <c r="B21" t="n">
-        <v>110298</v>
+        <v>8355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3152,31 +3144,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219677</v>
+        <v>106540</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3251,10 +3244,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845682</v>
+        <v>122845685</v>
       </c>
       <c r="B22" t="n">
-        <v>106032</v>
+        <v>110305</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3263,20 +3256,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>219677</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3362,10 +3355,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122845675</v>
+        <v>122845740</v>
       </c>
       <c r="B23" t="n">
-        <v>8355</v>
+        <v>100642</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3374,32 +3367,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,32 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68763726</v>
+        <v>78509776</v>
       </c>
       <c r="B3" t="n">
-        <v>102502</v>
+        <v>99590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>528</v>
+        <v>221333</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knippnejlika</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dianthus armeria</t>
+          <t>Trifolium montanum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,20 +827,23 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gamla Skogsby SV, Öl</t>
+          <t>Mörbylånga kommun, Kalmar län, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592412.7399681057</v>
+        <v>592484.6654673247</v>
       </c>
       <c r="R3" t="n">
-        <v>6275752.556139278</v>
+        <v>6275742.027430925</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,14 +868,9 @@
           <t>Torslunda</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Hö-Mör-5404</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -882,7 +880,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -902,23 +900,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Ennerfelt</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78509776</v>
+        <v>86544489</v>
       </c>
       <c r="B4" t="n">
         <v>99590</v>
@@ -951,26 +945,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörbylånga kommun, Kalmar län, Öl</t>
+          <t>Slingan Ölands skogsby, 530 m OSO Station Linné, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592484.6654673247</v>
+        <v>592466.6394818558</v>
       </c>
       <c r="R4" t="n">
-        <v>6275742.027430925</v>
+        <v>6275759.243350616</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +986,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1004,7 +996,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1018,25 +1010,26 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Robert Ennerfelt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Robert Ennerfelt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86544489</v>
+        <v>101731654</v>
       </c>
       <c r="B5" t="n">
         <v>99590</v>
@@ -1071,22 +1064,26 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slingan Ölands skogsby, 530 m OSO Station Linné, Öl</t>
+          <t>Gamla Skogsby, vid stig, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592466.6394818558</v>
+        <v>592465.8874176986</v>
       </c>
       <c r="R5" t="n">
-        <v>6275759.243350616</v>
+        <v>6275743.26606888</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1107,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1120,7 +1117,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1141,22 +1138,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Robert Ennerfelt</t>
+          <t>Lars Stibe</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Robert Ennerfelt</t>
+          <t>Lars Stibe</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101731654</v>
+        <v>109906083</v>
       </c>
       <c r="B6" t="n">
-        <v>99590</v>
+        <v>12292</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,45 +1166,56 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221333</v>
+        <v>101303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Svart majbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Meloe proscarabaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gamla Skogsby, vid stig, Öl</t>
+          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592465.8874176986</v>
+        <v>592520.0650462544</v>
       </c>
       <c r="R6" t="n">
-        <v>6275743.26606888</v>
+        <v>6275737.30151669</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1239,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2004-03-30</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1241,7 +1249,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1255,29 +1263,46 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>meadow with shrub vegetation</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
+          <t>Station Linné</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Stibe</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Station Linné, Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109906083</v>
+        <v>109906230</v>
       </c>
       <c r="B7" t="n">
-        <v>12292</v>
+        <v>8174</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,26 +1315,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101303</v>
+        <v>101201</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart majbagge</t>
+          <t>Blyvivel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meloe proscarabaeus</t>
+          <t>Lepyrus capucinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1363,7 +1388,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2004-03-30</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1373,7 +1398,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1423,10 +1448,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109906230</v>
+        <v>109928163</v>
       </c>
       <c r="B8" t="n">
-        <v>8174</v>
+        <v>26523</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,36 +1464,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101201</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Blyvivel</t>
-        </is>
+        <v>234775</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepyrus capucinus</t>
+          <t>Edwardsiana plebeja</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Edwards, 1914)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>ex.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1512,7 +1527,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2003-08-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1522,7 +1537,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2003-08-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1544,16 +1559,8 @@
           <t>meadow with shrub vegetation</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Bengt Andersson</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
           <t>Station Linné</t>
@@ -1561,7 +1568,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Station Linné, Bengt Andersson</t>
+          <t>Station Linné</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1572,10 +1579,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109928163</v>
+        <v>109928151</v>
       </c>
       <c r="B9" t="n">
-        <v>26523</v>
+        <v>26533</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1588,16 +1595,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>234775</v>
+        <v>250388</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Edwardsiana plebeja</t>
+          <t>Edwardsiana ulmiphagus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Edwards, 1914)</t>
+          <t>Wilson &amp; Claridge, 1999</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1651,17 +1658,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>2003-07-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>2003-08-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2003-08-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1703,10 +1710,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109928151</v>
+        <v>116299248</v>
       </c>
       <c r="B10" t="n">
-        <v>26533</v>
+        <v>12360</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,16 +1726,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>250388</v>
+        <v>101303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart majbagge</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Edwardsiana ulmiphagus</t>
+          <t>Meloe proscarabaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Wilson &amp; Claridge, 1999</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1736,29 +1748,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>malaisefälla</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
+          <t>Station Linné ost, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592520.0650462544</v>
+        <v>592447</v>
       </c>
       <c r="R10" t="n">
-        <v>6275737.30151669</v>
+        <v>6275748</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1782,22 +1793,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2003-07-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2003-08-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,38 +1807,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>meadow with shrub vegetation</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Station Linné</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Station Linné</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Svenska Malaisefälleprojektet</t>
-        </is>
-      </c>
+          <t>Björn Kinsten, Ingvar Landén, siv Toresson, Per Fogelström, Kirsten Malmström, Anders Sandsborg, Mats Henriksson, Tommy Carlström, Tomas Lundqvist, Tomas Burén, Stephanie Janowski, Ingela Carlström, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116299248</v>
+        <v>117955340</v>
       </c>
       <c r="B11" t="n">
-        <v>12360</v>
+        <v>102156</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1846,54 +1838,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101303</v>
+        <v>223248</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart majbagge</t>
+          <t>Lundalm</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meloe proscarabaeus</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Station Linné ost, Öl</t>
+          <t>Gamla Skogsby, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592447</v>
+        <v>592683</v>
       </c>
       <c r="R11" t="n">
-        <v>6275748</v>
+        <v>6275626</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1917,12 +1900,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1938,22 +1921,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>David Gustafsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Björn Kinsten, Ingvar Landén, siv Toresson, Per Fogelström, Kirsten Malmström, Anders Sandsborg, Mats Henriksson, Tommy Carlström, Tomas Lundqvist, Tomas Burén, Stephanie Janowski, Ingela Carlström, Ulla-Britt Andersson</t>
+          <t>David Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117955340</v>
+        <v>120862105</v>
       </c>
       <c r="B12" t="n">
-        <v>102156</v>
+        <v>90130</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,45 +1945,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223248</v>
+        <v>1589</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lundalm</t>
+          <t>Hårig jordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Geastrum melanocephalum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>(Czern.) V.J.Staněk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gamla Skogsby, Öl</t>
+          <t>Gamla skogsby, Station Linné, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592683</v>
+        <v>592472</v>
       </c>
       <c r="R12" t="n">
-        <v>6275626</v>
+        <v>6275775</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2024,12 +2006,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2045,22 +2027,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Gustafsson</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Gustafsson</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120862105</v>
+        <v>121374571</v>
       </c>
       <c r="B13" t="n">
-        <v>90130</v>
+        <v>18266</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2069,44 +2051,60 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1589</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hårig jordstjärna</t>
-        </is>
+        <v>241821</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Geastrum melanocephalum</t>
+          <t>Sciomyza testacea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Czern.) V.J.Staněk</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>Macquart, 1835</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gamla skogsby, Station Linné, Öl</t>
+          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592472</v>
+        <v>592520</v>
       </c>
       <c r="R13" t="n">
-        <v>6275775</v>
+        <v>6275737</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2130,12 +2128,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2005-08-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2005-08-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,29 +2142,43 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>meadow with shrub vegetation</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Station Linné</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121374571</v>
+        <v>121422006</v>
       </c>
       <c r="B14" t="n">
-        <v>18266</v>
+        <v>13870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2175,20 +2187,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>241821</v>
+        <v>101389</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gulbakig trädstyltfluga</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sciomyza testacea</t>
+          <t>Neurigona abdominalis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Macquart, 1835</t>
+          <t>(Fallén, 1823)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2208,7 +2225,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2252,12 +2269,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2005-08-19</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2274,9 +2291,9 @@
           <t>meadow with shrub vegetation</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>Station Linné</t>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr"/>
@@ -2299,10 +2316,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121422006</v>
+        <v>121421947</v>
       </c>
       <c r="B15" t="n">
-        <v>13870</v>
+        <v>13533</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,21 +2332,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101389</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Gulbakig trädstyltfluga</t>
-        </is>
+        <v>250187</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neurigona abdominalis</t>
+          <t>Achalcus bimaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fallén, 1823)</t>
+          <t>Pollet, 1996</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2393,12 +2405,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>2006-07-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2440,10 +2452,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121421947</v>
+        <v>121580128</v>
       </c>
       <c r="B16" t="n">
-        <v>13533</v>
+        <v>30226</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2456,16 +2468,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>250187</v>
+        <v>102645</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ängsvägstekel</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Achalcus bimaculatus</t>
+          <t>Priocnemis agilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pollet, 1996</t>
+          <t>(Shuckard, 1837)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2485,7 +2502,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2529,12 +2546,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2006-07-03</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2006-07-20</t>
+          <t>2004-08-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2551,13 +2568,22 @@
           <t>meadow with shrub vegetation</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Johan Abenius</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
       <c r="AW16" t="inlineStr">
         <is>
           <t>Station Linné</t>
@@ -2576,10 +2602,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121580128</v>
+        <v>121603374</v>
       </c>
       <c r="B17" t="n">
-        <v>30226</v>
+        <v>13428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2592,21 +2618,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102645</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ängsvägstekel</t>
-        </is>
+        <v>236243</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Priocnemis agilis</t>
+          <t>Myopa hirsuta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Shuckard, 1837)</t>
+          <t>Stuke &amp; Clements, 2008</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2670,12 +2691,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2005-04-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2004-08-23</t>
+          <t>2005-05-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2700,12 +2721,12 @@
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>Johan Abenius</t>
+          <t>Fredrik Östrand</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -2726,10 +2747,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121603374</v>
+        <v>121861066</v>
       </c>
       <c r="B18" t="n">
-        <v>13428</v>
+        <v>24795</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2738,20 +2759,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>236243</v>
+        <v>102058</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stumpvingeharkrank</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myopa hirsuta</t>
+          <t>Tipula autumnalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Stuke &amp; Clements, 2008</t>
+          <t>Loew, 1864</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2815,12 +2841,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2005-04-25</t>
+          <t>2006-08-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2005-05-20</t>
+          <t>2006-09-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2845,12 +2871,12 @@
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>Fredrik Östrand</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -2871,10 +2897,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121861066</v>
+        <v>122845685</v>
       </c>
       <c r="B19" t="n">
-        <v>24795</v>
+        <v>110308</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2883,65 +2909,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102058</v>
+        <v>219677</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stumpvingeharkrank</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tipula autumnalis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Loew, 1864</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>malaisefälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SMTP Trap ID 22, Gamla Skogsby (Kalkstad), Öl</t>
+          <t>Gamla skogsby, Station Linné, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592520</v>
+        <v>592472</v>
       </c>
       <c r="R19" t="n">
-        <v>6275737</v>
+        <v>6275775</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2965,12 +2975,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2006-08-15</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2006-09-06</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2979,52 +2989,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>meadow with shrub vegetation</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>Station Linné</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+      <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Station Linné</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Station Linné</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Svenska Malaisefälleprojektet</t>
-        </is>
-      </c>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122845685</v>
+        <v>122845675</v>
       </c>
       <c r="B20" t="n">
-        <v>110308</v>
+        <v>8355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3033,31 +3020,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219677</v>
+        <v>106540</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3132,10 +3120,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122845675</v>
+        <v>122845682</v>
       </c>
       <c r="B21" t="n">
-        <v>8355</v>
+        <v>106041</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3144,32 +3132,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3244,10 +3231,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122845682</v>
+        <v>122845740</v>
       </c>
       <c r="B22" t="n">
-        <v>106041</v>
+        <v>100645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3256,30 +3243,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
@@ -3352,125 +3347,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>122845740</v>
-      </c>
-      <c r="B23" t="n">
-        <v>100645</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Gamla skogsby, Station Linné, Öl</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>592472</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6275775</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Mörbylånga</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Torslunda</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Frank Pollari-Karlsson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Frank Pollari-Karlsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11163-2021 artfynd.xlsx
+++ b/artfynd/A 11163-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3348,6 +3348,224 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131528217</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58609</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gamla Skogsby, Station Linné, Öl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>592362</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6275804</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Robert Ennerfelt, Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131528215</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58609</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gamla Skogsby, Station Linné, Öl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>592397</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6275758</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Robert Ennerfelt, Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
